--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/09-caixa-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/09-caixa-da-clinica.xlsx
@@ -53329,10 +53329,10 @@
     <dataValidation sqref="B5:B1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Entrada,Saída"</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C1504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$H$5,0,0,MAX(1,COUNTA(Config!$D$5:$D$16)+COUNTA(Config!$F$5:$F$20)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D1504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$J$5,0,0,MAX(1,COUNTA(Config!$J$5:$J$34)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="H5:H1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -53341,10 +53341,10 @@
     <dataValidation sqref="I5:I1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Sim,Não"</formula1>
     </dataValidation>
-    <dataValidation sqref="A5:A1504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="A5:A1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation sqref="G5:G1504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="G5:G1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/09-caixa-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/09-caixa-da-clinica.xlsx
@@ -1035,7 +1035,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="J4" s="30" t="inlineStr">
         <is>
-          <t>Convênios e outros recebedores (até 30)</t>
+          <t>Convênios, pacientes e outros pagadores (sugestão, até 200)</t>
         </is>
       </c>
       <c r="L4" s="30" t="inlineStr">
@@ -2942,7 +2942,11 @@
         <f>IF(5&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,5),IF(5&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,5-COUNTA($D$5:$D$16)),""))</f>
         <v>Convênio · Vida Care</v>
       </c>
-      <c r="J9" s="31" t="n"/>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>Ana Costa</t>
+        </is>
+      </c>
       <c r="L9" s="34" t="inlineStr">
         <is>
           <t>Maio</t>
@@ -2964,7 +2968,11 @@
         <f>IF(6&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,6),IF(6&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,6-COUNTA($D$5:$D$16)),""))</f>
         <v>Outras entradas</v>
       </c>
-      <c r="J10" s="31" t="n"/>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>Beatriz Gomes</t>
+        </is>
+      </c>
       <c r="L10" s="34" t="inlineStr">
         <is>
           <t>Junho</t>
@@ -2982,7 +2990,11 @@
         <f>IF(7&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,7),IF(7&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,7-COUNTA($D$5:$D$16)),""))</f>
         <v>Pró-labore dos sócios</v>
       </c>
-      <c r="J11" s="31" t="n"/>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>Beatriz Gonçalves</t>
+        </is>
+      </c>
       <c r="L11" s="34" t="inlineStr">
         <is>
           <t>Julho</t>
@@ -3000,7 +3012,11 @@
         <f>IF(8&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,8),IF(8&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,8-COUNTA($D$5:$D$16)),""))</f>
         <v>Aluguel e condomínio</v>
       </c>
-      <c r="J12" s="31" t="n"/>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>Beatriz Monteiro</t>
+        </is>
+      </c>
       <c r="L12" s="34" t="inlineStr">
         <is>
           <t>Agosto</t>
@@ -3018,7 +3034,11 @@
         <f>IF(9&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,9),IF(9&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,9-COUNTA($D$5:$D$16)),""))</f>
         <v>Recepção (salário e encargos)</v>
       </c>
-      <c r="J13" s="31" t="n"/>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>Beatriz Reis</t>
+        </is>
+      </c>
       <c r="L13" s="34" t="inlineStr">
         <is>
           <t>Setembro</t>
@@ -3036,7 +3056,11 @@
         <f>IF(10&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,10),IF(10&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,10-COUNTA($D$5:$D$16)),""))</f>
         <v>Contador</v>
       </c>
-      <c r="J14" s="31" t="n"/>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>Bruno Carvalho</t>
+        </is>
+      </c>
       <c r="L14" s="34" t="inlineStr">
         <is>
           <t>Outubro</t>
@@ -3054,7 +3078,11 @@
         <f>IF(11&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,11),IF(11&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,11-COUNTA($D$5:$D$16)),""))</f>
         <v>Sistema de agenda e assinaturas</v>
       </c>
-      <c r="J15" s="31" t="n"/>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>Camila Batista</t>
+        </is>
+      </c>
       <c r="L15" s="34" t="inlineStr">
         <is>
           <t>Novembro</t>
@@ -3072,7 +3100,11 @@
         <f>IF(12&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,12),IF(12&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,12-COUNTA($D$5:$D$16)),""))</f>
         <v>Energia, água, internet e telefone</v>
       </c>
-      <c r="J16" s="31" t="n"/>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>Camila Dias</t>
+        </is>
+      </c>
       <c r="L16" s="34" t="inlineStr">
         <is>
           <t>Dezembro</t>
@@ -3089,7 +3121,11 @@
         <f>IF(13&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,13),IF(13&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,13-COUNTA($D$5:$D$16)),""))</f>
         <v>Limpeza e material de escritório</v>
       </c>
-      <c r="J17" s="31" t="n"/>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>Camila Freitas</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="F18" s="31" t="inlineStr">
@@ -3101,7 +3137,11 @@
         <f>IF(14&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,14),IF(14&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,14-COUNTA($D$5:$D$16)),""))</f>
         <v>Marketing e site</v>
       </c>
-      <c r="J18" s="31" t="n"/>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>Camila Martins</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="F19" s="31" t="inlineStr">
@@ -3113,7 +3153,11 @@
         <f>IF(15&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,15),IF(15&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,15-COUNTA($D$5:$D$16)),""))</f>
         <v>Anuidade CRM, seguro e cursos</v>
       </c>
-      <c r="J19" s="31" t="n"/>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Barros</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="F20" s="31" t="n"/>
@@ -3121,97 +3165,171 @@
         <f>IF(16&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,16),IF(16&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,16-COUNTA($D$5:$D$16)),""))</f>
         <v>Materiais e insumos de atendimento</v>
       </c>
-      <c r="J20" s="31" t="n"/>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Castro</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="H21" s="33" t="str">
         <f>IF(17&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,17),IF(17&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,17-COUNTA($D$5:$D$16)),""))</f>
         <v>Taxas de cartão</v>
       </c>
-      <c r="J21" s="31" t="n"/>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Fernandes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="H22" s="33" t="str">
         <f>IF(18&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,18),IF(18&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,18-COUNTA($D$5:$D$16)),""))</f>
         <v>Repasse à médica parceira</v>
       </c>
-      <c r="J22" s="31" t="n"/>
+      <c r="J22" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Freitas</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="H23" s="33" t="str">
         <f>IF(19&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,19),IF(19&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,19-COUNTA($D$5:$D$16)),""))</f>
         <v>Manutenção de equipamentos</v>
       </c>
-      <c r="J23" s="31" t="n"/>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Gomes</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="H24" s="33" t="str">
         <f>IF(20&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,20),IF(20&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,20-COUNTA($D$5:$D$16)),""))</f>
         <v>Impostos e taxas</v>
       </c>
-      <c r="J24" s="31" t="n"/>
+      <c r="J24" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Gonçalves</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="H25" s="33" t="str">
         <f>IF(21&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,21),IF(21&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,21-COUNTA($D$5:$D$16)),""))</f>
         <v>Outras saídas</v>
       </c>
-      <c r="J25" s="31" t="n"/>
+      <c r="J25" s="31" t="inlineStr">
+        <is>
+          <t>Carlos Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="H26" s="33">
         <f>IF(22&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,22),IF(22&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,22-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J26" s="31" t="n"/>
+      <c r="J26" s="31" t="inlineStr">
+        <is>
+          <t>Cláudia Castro</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="H27" s="33">
         <f>IF(23&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,23),IF(23&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,23-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J27" s="31" t="n"/>
+      <c r="J27" s="31" t="inlineStr">
+        <is>
+          <t>Cláudia Costa</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="H28" s="33">
         <f>IF(24&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,24),IF(24&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,24-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J28" s="31" t="n"/>
+      <c r="J28" s="31" t="inlineStr">
+        <is>
+          <t>Cláudia Melo</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="H29" s="33">
         <f>IF(25&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,25),IF(25&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,25-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J29" s="31" t="n"/>
+      <c r="J29" s="31" t="inlineStr">
+        <is>
+          <t>Cláudia Santos</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="H30" s="33">
         <f>IF(26&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,26),IF(26&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,26-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J30" s="31" t="n"/>
+      <c r="J30" s="31" t="inlineStr">
+        <is>
+          <t>Cláudia Vieira</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="H31" s="33">
         <f>IF(27&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,27),IF(27&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,27-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J31" s="31" t="n"/>
+      <c r="J31" s="31" t="inlineStr">
+        <is>
+          <t>Daniel Almeida</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="H32" s="33">
         <f>IF(28&lt;=COUNTA($D$5:$D$16),INDEX($D$5:$D$16,28),IF(28&lt;=COUNTA($D$5:$D$16)+COUNTA($F$5:$F$20),INDEX($F$5:$F$20,28-COUNTA($D$5:$D$16)),""))</f>
         <v/>
       </c>
-      <c r="J32" s="31" t="n"/>
+      <c r="J32" s="31" t="inlineStr">
+        <is>
+          <t>Daniel Melo</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="J33" s="31" t="n"/>
+      <c r="J33" s="31" t="inlineStr">
+        <is>
+          <t>Daniel Moreira</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="J34" s="31" t="n"/>
+      <c r="J34" s="31" t="inlineStr">
+        <is>
+          <t>Débora Machado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="J35" s="31" t="inlineStr">
+        <is>
+          <t>Débora Moreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" s="31" t="inlineStr">
+        <is>
+          <t>Débora Ramos</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="38" t="inlineStr">
@@ -3219,6 +3337,11 @@
           <t>Preencha categorias e recebedores de cima para baixo, sem pular linha: as listas suspensas de Lançamentos param na última linha preenchida.</t>
         </is>
       </c>
+      <c r="J37" s="31" t="inlineStr">
+        <is>
+          <t>Eduardo Lima</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="38" t="inlineStr">
@@ -3226,6 +3349,11 @@
           <t>Saldo antes do 1º lançamento: o que havia na conta da clínica na data do primeiro lançamento (no exemplo, 01/01/2026).</t>
         </is>
       </c>
+      <c r="J38" s="31" t="inlineStr">
+        <is>
+          <t>Eduardo Nunes</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="38" t="inlineStr">
@@ -3233,6 +3361,11 @@
           <t>Particular à vista entra pelo fechamento do dia (uma linha por dia e forma de pagamento; o detalhe por paciente fica na agenda 01). Particular a prazo entra por paciente, quando a parcela é paga (14). Convênio entra por lote pago (13).</t>
         </is>
       </c>
+      <c r="J39" s="31" t="inlineStr">
+        <is>
+          <t>Eduardo Pereira</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="38" t="inlineStr">
@@ -3240,6 +3373,11 @@
           <t>A receber (Pago? = Não): parcelas a prazo (14) e lotes de convênio enviados (13) com previsão de recebimento até o fim do mês de referência — vencidos e a vencer. O que tem previsão para depois do fim do mês fica fora e entra quando aquele mês chegar. Por isso "A receber" do Painel é menor que a soma do total em aberto da 13 com o da 14: aquelas duas olham a carteira inteira, esta olha o mês.</t>
         </is>
       </c>
+      <c r="J40" s="31" t="inlineStr">
+        <is>
+          <t>Eduardo Reis</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="38" t="inlineStr">
@@ -3247,6 +3385,11 @@
           <t>Quem lança: a RECEPÇÃO lança o fechamento do dia todo dia, no fechamento (planilha 04 · Checklist do dia). Na sexta, a sócia só CONFERE os cinco fechamentos da semana contra o extrato e marca o que caiu na conta (planilha 03 · Rotina da semana).</t>
         </is>
       </c>
+      <c r="J41" s="31" t="inlineStr">
+        <is>
+          <t>Elaine Cardoso</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="38" t="inlineStr">
@@ -3254,6 +3397,985 @@
           <t>Cartão: lance o valor bruto na data em que ele CAI NA CONTA, não no dia da venda (a planilha 16 calcula essa data por venda e por parcela: débito no dia seguinte, crédito em 30 dias, parcelado de 30 em 30) e, no fim do mês, uma saída "Taxas de cartão" com o total das taxas que caíram nesse mês. Lançar cartão no dia da venda faz o saldo mostrar dinheiro que ainda não entrou. Repasse à médica parceira é a saída do dia 10 (planilha 11). Lançamentos pagos do exemplo vão até 11/09/2026 (a última sexta).</t>
         </is>
       </c>
+      <c r="J42" s="31" t="inlineStr">
+        <is>
+          <t>Elaine Xavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="J43" s="31" t="inlineStr">
+        <is>
+          <t>Fernanda Freitas</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="J44" s="31" t="inlineStr">
+        <is>
+          <t>Fernanda Gonçalves</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="J45" s="31" t="inlineStr">
+        <is>
+          <t>Fernanda Nunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="J46" s="31" t="inlineStr">
+        <is>
+          <t>Fábio Correia</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="J47" s="31" t="inlineStr">
+        <is>
+          <t>Fábio Ferreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="J48" s="31" t="inlineStr">
+        <is>
+          <t>Fábio Gomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="J49" s="31" t="inlineStr">
+        <is>
+          <t>Fábio Machado</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="J50" s="31" t="inlineStr">
+        <is>
+          <t>Fábio Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="J51" s="31" t="inlineStr">
+        <is>
+          <t>Gabriel Fernandes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="J52" s="31" t="inlineStr">
+        <is>
+          <t>Gabriel Lopes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="J53" s="31" t="inlineStr">
+        <is>
+          <t>Gabriel Oliveira</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="J54" s="31" t="inlineStr">
+        <is>
+          <t>Gabriel Reis</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="J55" s="31" t="inlineStr">
+        <is>
+          <t>Gabriel Vieira</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="J56" s="31" t="inlineStr">
+        <is>
+          <t>Gisele Lima</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="J57" s="31" t="inlineStr">
+        <is>
+          <t>Gisele Lopes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="J58" s="31" t="inlineStr">
+        <is>
+          <t>Gisele Pinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="J59" s="31" t="inlineStr">
+        <is>
+          <t>Gisele Ribeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="J60" s="31" t="inlineStr">
+        <is>
+          <t>Gisele Xavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="J61" s="31" t="inlineStr">
+        <is>
+          <t>Gustavo Barbosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="J62" s="31" t="inlineStr">
+        <is>
+          <t>Gustavo Carvalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="J63" s="31" t="inlineStr">
+        <is>
+          <t>Gustavo Ferreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="J64" s="31" t="inlineStr">
+        <is>
+          <t>Gustavo Pinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="J65" s="31" t="inlineStr">
+        <is>
+          <t>Helena Moreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="J66" s="31" t="inlineStr">
+        <is>
+          <t>Helena Ribeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="J67" s="31" t="inlineStr">
+        <is>
+          <t>Henrique Ribeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="J68" s="31" t="inlineStr">
+        <is>
+          <t>Henrique Santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="J69" s="31" t="inlineStr">
+        <is>
+          <t>Isabela Barbosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="J70" s="31" t="inlineStr">
+        <is>
+          <t>Isabela Nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="J71" s="31" t="inlineStr">
+        <is>
+          <t>Isabela Pinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="J72" s="31" t="inlineStr">
+        <is>
+          <t>Isabela Xavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="J73" s="31" t="inlineStr">
+        <is>
+          <t>Juliana Ribeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="J74" s="31" t="inlineStr">
+        <is>
+          <t>Juliana Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="J75" s="31" t="inlineStr">
+        <is>
+          <t>Larissa Costa</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="J76" s="31" t="inlineStr">
+        <is>
+          <t>Leandro Cardoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="J77" s="31" t="inlineStr">
+        <is>
+          <t>Leandro Ferreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="J78" s="31" t="inlineStr">
+        <is>
+          <t>Leandro Gomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="J79" s="31" t="inlineStr">
+        <is>
+          <t>Leandro Oliveira</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="J80" s="31" t="inlineStr">
+        <is>
+          <t>Letícia Vieira</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="J81" s="31" t="inlineStr">
+        <is>
+          <t>Lucas Cardoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="J82" s="31" t="inlineStr">
+        <is>
+          <t>Lucas Lopes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="J83" s="31" t="inlineStr">
+        <is>
+          <t>Lucas Xavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="J84" s="31" t="inlineStr">
+        <is>
+          <t>Marcelo Ferreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="J85" s="31" t="inlineStr">
+        <is>
+          <t>Marcelo Moreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="J86" s="31" t="inlineStr">
+        <is>
+          <t>Marcelo Santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="J87" s="31" t="inlineStr">
+        <is>
+          <t>Mariana Gomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="J88" s="31" t="inlineStr">
+        <is>
+          <t>Mariana Nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="J89" s="31" t="inlineStr">
+        <is>
+          <t>Mariana Reis</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="J90" s="31" t="inlineStr">
+        <is>
+          <t>Mateus Dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="J91" s="31" t="inlineStr">
+        <is>
+          <t>Mateus Lima</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="J92" s="31" t="inlineStr">
+        <is>
+          <t>Mateus Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="J93" s="31" t="inlineStr">
+        <is>
+          <t>Márcia Duarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="J94" s="31" t="inlineStr">
+        <is>
+          <t>Mônica Almeida</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="J95" s="31" t="inlineStr">
+        <is>
+          <t>Mônica Batista</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="J96" s="31" t="inlineStr">
+        <is>
+          <t>Mônica Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="J97" s="31" t="inlineStr">
+        <is>
+          <t>Mônica Pinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="J98" s="31" t="inlineStr">
+        <is>
+          <t>Mônica Teixeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="J99" s="31" t="inlineStr">
+        <is>
+          <t>Natália Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="J100" s="31" t="inlineStr">
+        <is>
+          <t>Natália Xavier</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="J101" s="31" t="inlineStr">
+        <is>
+          <t>Otávio Cardoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="J102" s="31" t="inlineStr">
+        <is>
+          <t>Otávio Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="J103" s="31" t="inlineStr">
+        <is>
+          <t>Otávio Nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="J104" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Correia</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="J105" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="J106" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Fernandes</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="J107" s="31" t="inlineStr">
+        <is>
+          <t>Patrícia Vieira</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="J108" s="31" t="inlineStr">
+        <is>
+          <t>Paulo Fernandes</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="J109" s="31" t="inlineStr">
+        <is>
+          <t>Paulo Freitas</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="J110" s="31" t="inlineStr">
+        <is>
+          <t>Paulo Nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="J111" s="31" t="inlineStr">
+        <is>
+          <t>Paulo Reis</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="J112" s="31" t="inlineStr">
+        <is>
+          <t>Paulo Ribeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="J113" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Carvalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="J114" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Castro</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="J115" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="J116" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Nunes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="J117" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Pinto</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="J118" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Reis</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="J119" s="31" t="inlineStr">
+        <is>
+          <t>Priscila Rocha</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="J120" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Araújo</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="J121" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Barros</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="J122" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Batista</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="J123" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Correia</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="J124" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="J125" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Nascimento</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="J126" s="31" t="inlineStr">
+        <is>
+          <t>Rafael Pereira</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="J127" s="31" t="inlineStr">
+        <is>
+          <t>Regina Castro</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="J128" s="31" t="inlineStr">
+        <is>
+          <t>Regina Duarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="J129" s="31" t="inlineStr">
+        <is>
+          <t>Regina Macedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="J130" s="31" t="inlineStr">
+        <is>
+          <t>Regina Teixeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="J131" s="31" t="inlineStr">
+        <is>
+          <t>Renato Dias</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="J132" s="31" t="inlineStr">
+        <is>
+          <t>Renato Pereira</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="J133" s="31" t="inlineStr">
+        <is>
+          <t>Ricardo Melo</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="J134" s="31" t="inlineStr">
+        <is>
+          <t>Roberta Almeida</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="J135" s="31" t="inlineStr">
+        <is>
+          <t>Roberta Araújo</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="J136" s="31" t="inlineStr">
+        <is>
+          <t>Roberta Fernandes</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="J137" s="31" t="inlineStr">
+        <is>
+          <t>Roberta Lima</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="J138" s="31" t="inlineStr">
+        <is>
+          <t>Rodrigo Cardoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="J139" s="31" t="inlineStr">
+        <is>
+          <t>Rodrigo Gomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="J140" s="31" t="inlineStr">
+        <is>
+          <t>Rodrigo Moreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="J141" s="31" t="inlineStr">
+        <is>
+          <t>Rodrigo Teixeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="J142" s="31" t="inlineStr">
+        <is>
+          <t>Sandra Barros</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="J143" s="31" t="inlineStr">
+        <is>
+          <t>Sandra Cardoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="J144" s="31" t="inlineStr">
+        <is>
+          <t>Sandra Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="J145" s="31" t="inlineStr">
+        <is>
+          <t>Simone Monteiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="J146" s="31" t="inlineStr">
+        <is>
+          <t>Sérgio Batista</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="J147" s="31" t="inlineStr">
+        <is>
+          <t>Sérgio Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="J148" s="31" t="inlineStr">
+        <is>
+          <t>Sérgio Teixeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="J149" s="31" t="inlineStr">
+        <is>
+          <t>Tatiana Cunha</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="J150" s="31" t="inlineStr">
+        <is>
+          <t>Tatiana Gonçalves</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="J151" s="31" t="inlineStr">
+        <is>
+          <t>Tatiana Macedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="J152" s="31" t="inlineStr">
+        <is>
+          <t>Tatiana Rocha</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="J153" s="31" t="inlineStr">
+        <is>
+          <t>Thiago Duarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="J154" s="31" t="inlineStr">
+        <is>
+          <t>Thiago Melo</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="J155" s="31" t="inlineStr">
+        <is>
+          <t>Vanessa Carvalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="J156" s="31" t="inlineStr">
+        <is>
+          <t>Vanessa Moreira</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="J157" s="31" t="inlineStr">
+        <is>
+          <t>Vinícius Cardoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="J158" s="31" t="inlineStr">
+        <is>
+          <t>Viviane Duarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="J159" s="31" t="inlineStr">
+        <is>
+          <t>Viviane Ribeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="J160" s="31" t="inlineStr">
+        <is>
+          <t>Viviane Teixeira</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="J161" s="31" t="inlineStr">
+        <is>
+          <t>Wagner Carvalho</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="J162" s="31" t="inlineStr">
+        <is>
+          <t>Wagner Costa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="J163" s="31" t="inlineStr">
+        <is>
+          <t>Wagner Lima</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="J164" s="31" t="inlineStr">
+        <is>
+          <t>Wagner Santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="J165" s="31" t="n"/>
+    </row>
+    <row r="166">
+      <c r="J166" s="31" t="n"/>
+    </row>
+    <row r="167">
+      <c r="J167" s="31" t="n"/>
+    </row>
+    <row r="168">
+      <c r="J168" s="31" t="n"/>
+    </row>
+    <row r="169">
+      <c r="J169" s="31" t="n"/>
+    </row>
+    <row r="170">
+      <c r="J170" s="31" t="n"/>
+    </row>
+    <row r="171">
+      <c r="J171" s="31" t="n"/>
+    </row>
+    <row r="172">
+      <c r="J172" s="31" t="n"/>
+    </row>
+    <row r="173">
+      <c r="J173" s="31" t="n"/>
+    </row>
+    <row r="174">
+      <c r="J174" s="31" t="n"/>
+    </row>
+    <row r="175">
+      <c r="J175" s="31" t="n"/>
+    </row>
+    <row r="176">
+      <c r="J176" s="31" t="n"/>
+    </row>
+    <row r="177">
+      <c r="J177" s="31" t="n"/>
+    </row>
+    <row r="178">
+      <c r="J178" s="31" t="n"/>
+    </row>
+    <row r="179">
+      <c r="J179" s="31" t="n"/>
+    </row>
+    <row r="180">
+      <c r="J180" s="31" t="n"/>
+    </row>
+    <row r="181">
+      <c r="J181" s="31" t="n"/>
+    </row>
+    <row r="182">
+      <c r="J182" s="31" t="n"/>
+    </row>
+    <row r="183">
+      <c r="J183" s="31" t="n"/>
+    </row>
+    <row r="184">
+      <c r="J184" s="31" t="n"/>
+    </row>
+    <row r="185">
+      <c r="J185" s="31" t="n"/>
+    </row>
+    <row r="186">
+      <c r="J186" s="31" t="n"/>
+    </row>
+    <row r="187">
+      <c r="J187" s="31" t="n"/>
+    </row>
+    <row r="188">
+      <c r="J188" s="31" t="n"/>
+    </row>
+    <row r="189">
+      <c r="J189" s="31" t="n"/>
+    </row>
+    <row r="190">
+      <c r="J190" s="31" t="n"/>
+    </row>
+    <row r="191">
+      <c r="J191" s="31" t="n"/>
+    </row>
+    <row r="192">
+      <c r="J192" s="31" t="n"/>
+    </row>
+    <row r="193">
+      <c r="J193" s="31" t="n"/>
+    </row>
+    <row r="194">
+      <c r="J194" s="31" t="n"/>
+    </row>
+    <row r="195">
+      <c r="J195" s="31" t="n"/>
+    </row>
+    <row r="196">
+      <c r="J196" s="31" t="n"/>
+    </row>
+    <row r="197">
+      <c r="J197" s="31" t="n"/>
+    </row>
+    <row r="198">
+      <c r="J198" s="31" t="n"/>
+    </row>
+    <row r="199">
+      <c r="J199" s="31" t="n"/>
+    </row>
+    <row r="200">
+      <c r="J200" s="31" t="n"/>
+    </row>
+    <row r="201">
+      <c r="J201" s="31" t="n"/>
+    </row>
+    <row r="202">
+      <c r="J202" s="31" t="n"/>
+    </row>
+    <row r="203">
+      <c r="J203" s="31" t="n"/>
+    </row>
+    <row r="204">
+      <c r="J204" s="31" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -53332,8 +54454,8 @@
     <dataValidation sqref="C5:C1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$H$5,0,0,MAX(1,COUNTA(Config!$D$5:$D$16)+COUNTA(Config!$F$5:$F$20)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>=OFFSET(Config!$J$5,0,0,MAX(1,COUNTA(Config!$J$5:$J$34)),1)</formula1>
+    <dataValidation sqref="D5:D1504" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=OFFSET(Config!$J$5,0,0,MAX(1,COUNTA(Config!$J$5:$J$204)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="H5:H1504" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"Pix,Dinheiro,Cartão de débito,Cartão de crédito,Transferência,Boleto"</formula1>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/09-caixa-da-clinica.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/09-caixa-da-clinica.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D19" s="24">
         <f>IF(Config!$F$15="","",IF(Config!$B$7=1,SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,12,Lançamentos!$K$5:$K$1504,Config!$B$5-1,Lançamentos!$C$5:$C$1504,Config!$F$15),SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,Config!$B$7-1,Lançamentos!$K$5:$K$1504,Config!$B$5,Lançamentos!$C$5:$C$1504,Config!$F$15)))</f>
-        <v>681.61</v>
+        <v>681.6</v>
       </c>
       <c r="E19" s="24">
         <f>IF(Config!$F$15="","",SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$C$5:$C$1504,Config!$F$15,Lançamentos!$K$5:$K$1504,Config!$B$5,Lançamentos!$J$5:$J$1504,"&lt;="&amp;Config!$B$7))</f>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="D25" s="28">
         <f>SUM(D9:D24)</f>
-        <v>40868.61</v>
+        <v>40868.6</v>
       </c>
       <c r="E25" s="28">
         <f>SUM(E9:E24)</f>
@@ -2389,15 +2389,15 @@
       </c>
       <c r="C57" s="24">
         <f>SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,2,Lançamentos!$K$5:$K$1504,Config!$B$5)</f>
-        <v>36230.54</v>
+        <v>36230.55</v>
       </c>
       <c r="D57" s="24">
         <f>B57-C57</f>
-        <v>-10580.54</v>
+        <v>-10580.55</v>
       </c>
       <c r="E57" s="24">
         <f>Config!$B$8+SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Entrada",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,3,0))-SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,3,0))</f>
-        <v>4797.41</v>
+        <v>4797.39999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E58" s="24">
         <f>Config!$B$8+SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Entrada",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,4,0))-SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,4,0))</f>
-        <v>7086.28</v>
+        <v>7086.27</v>
       </c>
     </row>
     <row r="59">
@@ -2435,15 +2435,15 @@
       </c>
       <c r="C59" s="24">
         <f>SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,4,Lançamentos!$K$5:$K$1504,Config!$B$5)</f>
-        <v>40254.1</v>
+        <v>40254.11</v>
       </c>
       <c r="D59" s="24">
         <f>B59-C59</f>
-        <v>520.900000000002</v>
+        <v>520.889999999999</v>
       </c>
       <c r="E59" s="24">
         <f>Config!$B$8+SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Entrada",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,5,0))-SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,5,0))</f>
-        <v>7607.17999999999</v>
+        <v>7607.16</v>
       </c>
     </row>
     <row r="60">
@@ -2458,11 +2458,11 @@
       </c>
       <c r="C60" s="24">
         <f>SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,5,Lançamentos!$K$5:$K$1504,Config!$B$5)</f>
-        <v>40120.29</v>
+        <v>40120.27</v>
       </c>
       <c r="D60" s="24">
         <f>B60-C60</f>
-        <v>5259.71</v>
+        <v>5259.73</v>
       </c>
       <c r="E60" s="24">
         <f>Config!$B$8+SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Entrada",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,6,0))-SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,6,0))</f>
@@ -2504,15 +2504,15 @@
       </c>
       <c r="C62" s="24">
         <f>SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,7,Lançamentos!$K$5:$K$1504,Config!$B$5)</f>
-        <v>46321.6</v>
+        <v>46321.61</v>
       </c>
       <c r="D62" s="24">
         <f>B62-C62</f>
-        <v>-1850.6</v>
+        <v>-1850.61</v>
       </c>
       <c r="E62" s="24">
         <f>Config!$B$8+SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Entrada",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,8,0))-SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,8,0))</f>
-        <v>16553.42</v>
+        <v>16553.41</v>
       </c>
     </row>
     <row r="63">
@@ -2527,11 +2527,11 @@
       </c>
       <c r="C63" s="24">
         <f>SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$J$5:$J$1504,8,Lançamentos!$K$5:$K$1504,Config!$B$5)</f>
-        <v>40868.61</v>
+        <v>40868.6</v>
       </c>
       <c r="D63" s="24">
         <f>B63-C63</f>
-        <v>14972.39</v>
+        <v>14972.4</v>
       </c>
       <c r="E63" s="24">
         <f>Config!$B$8+SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Entrada",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,9,0))-SUMIFS(Lançamentos!$G$5:$G$1504,Lançamentos!$B$5:$B$1504,"Saída",Lançamentos!$I$5:$I$1504,"Sim",Lançamentos!$A$5:$A$1504,"&lt;="&amp;DATE(Config!$B$5,9,0))</f>
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="G117" s="36" t="n">
-        <v>281.54</v>
+        <v>281.55</v>
       </c>
       <c r="H117" s="32" t="inlineStr">
         <is>
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="G291" s="36" t="n">
-        <v>485.1</v>
+        <v>485.11</v>
       </c>
       <c r="H291" s="32" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         </is>
       </c>
       <c r="G381" s="36" t="n">
-        <v>478.29</v>
+        <v>478.27</v>
       </c>
       <c r="H381" s="32" t="inlineStr">
         <is>
@@ -31441,7 +31441,7 @@
         </is>
       </c>
       <c r="G575" s="36" t="n">
-        <v>346.6</v>
+        <v>346.61</v>
       </c>
       <c r="H575" s="32" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         </is>
       </c>
       <c r="G675" s="36" t="n">
-        <v>681.61</v>
+        <v>681.6</v>
       </c>
       <c r="H675" s="32" t="inlineStr">
         <is>
